--- a/req_doc_formats/students.xlsx
+++ b/req_doc_formats/students.xlsx
@@ -430,20 +430,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,50 +457,65 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>APAAR ID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>First Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Last Name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Class</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Section</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Roll No</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Date of Birth</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Gender</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Father Name</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Mother Name</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Parent Phone</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Hosteler</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Transport</t>
         </is>
@@ -511,50 +529,65 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>123456789012</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>Kabir</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Singh</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Grade 6</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>2013-05-12</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Arjun Singh</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Meera Singh</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>9876543210</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -568,50 +601,65 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>123456789013</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>Priya</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Sharma</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Grade 6</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>2013-08-22</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Vikram Sharma</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Anita Sharma</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>9876543211</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -625,59 +673,75 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>123456789014</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>Rohan</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Verma</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Grade 7</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>2012-11-03</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Suresh Verma</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Kavita Verma</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>9876543212</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Hosteler: Yes/No | Transport: Yes/No | Gender: M or F | Date: YYYY-MM-DD</t>
+          <t>Hosteler: Yes/No | Transport: Yes/No | Gender: M or F | Date: YYYY-MM-DD | APAAR ID: 12-digit student ID</t>
         </is>
       </c>
     </row>
